--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2022_valparaiso.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2022_valparaiso.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:45</t>
+    <t xml:space="preserve">2026-09-24 01:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -999,7 +999,7 @@
         <v>-0.75</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>-0.05</v>
@@ -1022,7 +1022,7 @@
         <v>-0.23</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>-0.08</v>
@@ -1045,7 +1045,7 @@
         <v>-0.64</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>-0.06</v>
@@ -1065,13 +1065,13 @@
         <v>36</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-0.4</v>
+        <v>-0.41</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="24">
@@ -1105,19 +1105,19 @@
         <v>35</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>-0.58</v>
+        <v>0.06</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>36</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>-0.38</v>
+        <v>-0.23</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>329</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>-0.2</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="26">
@@ -1134,13 +1134,13 @@
         <v>36</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>329</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-0.55</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="27">
@@ -1151,19 +1151,19 @@
         <v>35</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>-0.44</v>
+        <v>0.01</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>36</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.13</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>329</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>-0.23</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="28">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2022_valparaiso.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2022_valparaiso.xlsx
@@ -126,7 +126,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:35</t>
+    <t xml:space="preserve">2026-10-01 23:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2022_valparaiso.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2022_valparaiso.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:22</t>
+    <t xml:space="preserve">2026-10-05 19:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
